--- a/Exam/gymtrackerpro/lib/controller/__tests__/bbt/user-controller/createMember-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/bbt/user-controller/createMember-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="127">
-  <si>
-    <t>Statement: user-controller.createMember(data) – Server Action. Validates CreateMemberInput via createMemberSchema (email, fullName ≥8 chars, phone E.164, dateOfBirth past, password ≥8, membershipStart ISO date). On valid input delegates to userService.createMember(). Returns ActionResult&lt;MemberWithUser&gt;.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="181">
+  <si>
+    <t>Statement: createMember(data) – Validates the create-member input and returns an ActionResult&lt;MemberWithUser&gt;. Returns success with the created MemberWithUser on success. Returns a field-level validation error for schema failures without calling the service. Returns a failure with the service error message for ConflictError and TransactionError. Whitespace is trimmed from email, fullName, and phone before validation. fullName must be 8–64 characters after trimming and must not be whitespace-only. Password must be 8–64 characters with at least one uppercase letter, one digit, and one special character. dateOfBirth must be in YYYY-MM-DD format and must be strictly in the past (before today). membershipStart must be in YYYY-MM-DD format; future dates are accepted.</t>
   </si>
   <si>
     <t/>
@@ -31,27 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: CreateMemberInput { email, fullName, phone, dateOfBirth, password, membershipStart }</t>
+    <t>Input: data: CreateMemberInput { email, fullName, phone, dateOfBirth, password, membershipStart, ...optional }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>userService.createMember is mock-injected</t>
+    <t>Password rules: 8–64 chars, at least one uppercase letter, one digit, one special character. fullName rules: 8–64 chars after trim, not whitespace-only. dateOfBirth: YYYY-MM-DD, strictly before today. membershipStart: YYYY-MM-DD, any date including future.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: ActionResult&lt;MemberWithUser&gt;</t>
+    <t>Output: Promise&lt;ActionResult&lt;MemberWithUser&gt;&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t xml:space="preserve">On success: returns MemberWithUser.
-On validation failure: returns errors, no service call.
-On AppError: returns message.</t>
+    <t>On success: member created successfully, returned data matches the created member. On validation failure: field-level validation error returned, the service is not called. On service error: operation fails with the service error message.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -66,211 +64,439 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>all fields valid</t>
-  </si>
-  <si>
-    <t>All fields pass schema validation</t>
+    <t>Input validity</t>
+  </si>
+  <si>
+    <t>All fields valid → member created successfully, returned data matches the created member</t>
+  </si>
+  <si>
+    <t>Required fields</t>
+  </si>
+  <si>
+    <t>Missing email → validation fails: email field error returned</t>
+  </si>
+  <si>
+    <t>Missing fullName → validation fails: fullName field error returned</t>
+  </si>
+  <si>
+    <t>Missing phone → validation fails: phone field error returned</t>
+  </si>
+  <si>
+    <t>Missing dateOfBirth → validation fails: dateOfBirth field error returned</t>
+  </si>
+  <si>
+    <t>Missing password → validation fails: password field error returned</t>
+  </si>
+  <si>
+    <t>Missing membershipStart → validation fails: membershipStart field error returned</t>
+  </si>
+  <si>
+    <t>Email format</t>
+  </si>
+  <si>
+    <t>Invalid email format ("invalid") → validation fails: email field error returned</t>
+  </si>
+  <si>
+    <t>Password rules</t>
+  </si>
+  <si>
+    <t>No uppercase letter ("securep@ss1!") → validation fails: password field error returned</t>
+  </si>
+  <si>
+    <t>No digit ("SecurePass!") → validation fails: password field error returned</t>
+  </si>
+  <si>
+    <t>No special character ("SecurePass1") → validation fails: password field error returned</t>
+  </si>
+  <si>
+    <t>Phone format</t>
+  </si>
+  <si>
+    <t>Invalid phone format ("0712345678", missing country code) → validation fails: phone field error returned</t>
+  </si>
+  <si>
+    <t>dateOfBirth format</t>
+  </si>
+  <si>
+    <t>Invalid format ("15-01-1990", not YYYY-MM-DD) → validation fails: dateOfBirth field error returned</t>
+  </si>
+  <si>
+    <t>dateOfBirth value</t>
+  </si>
+  <si>
+    <t>Future dateOfBirth ("2099-01-01") → validation fails: dateOfBirth field error returned</t>
+  </si>
+  <si>
+    <t>membershipStart</t>
+  </si>
+  <si>
+    <t>Future membershipStart ("2099-01-01") → validation passes, member created successfully (future dates accepted)</t>
+  </si>
+  <si>
+    <t>Invalid membershipStart format ("01/01/2024") → validation fails: membershipStart field error returned</t>
+  </si>
+  <si>
+    <t>fullName content</t>
+  </si>
+  <si>
+    <t>fullName whitespace-only ("         ") → validation fails: fullName field error returned</t>
+  </si>
+  <si>
+    <t>Whitespace trimming</t>
+  </si>
+  <si>
+    <t>fullName with surrounding whitespace ("  John Doe Test  ") → trimmed and accepted, member created successfully</t>
+  </si>
+  <si>
+    <t>email with surrounding whitespace ("  john.doe@example.com  ") → trimmed and accepted, member created successfully</t>
+  </si>
+  <si>
+    <t>phone with surrounding whitespace ("  +40712345678  ") → trimmed and accepted, member created successfully</t>
+  </si>
+  <si>
+    <t>Service error</t>
+  </si>
+  <si>
+    <t>A duplicate email conflict occurs → operation fails with message "Email already registered"</t>
+  </si>
+  <si>
+    <t>A database transaction failure occurs → operation fails with message "DB failure"</t>
+  </si>
+  <si>
+    <t>No TC</t>
+  </si>
+  <si>
+    <t>EC</t>
+  </si>
+  <si>
+    <t>Input Data</t>
+  </si>
+  <si>
+    <t>Expected</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>all required member fields provided with valid values</t>
+  </si>
+  <si>
+    <t>member created successfully, returned data matches the created member</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>valid member data with email field omitted</t>
+  </si>
+  <si>
+    <t>validation fails: email field error returned</t>
+  </si>
+  <si>
+    <t>EC-3</t>
+  </si>
+  <si>
+    <t>valid member data with fullName field omitted</t>
+  </si>
+  <si>
+    <t>validation fails: fullName field error returned</t>
+  </si>
+  <si>
+    <t>EC-4</t>
+  </si>
+  <si>
+    <t>valid member data with phone field omitted</t>
+  </si>
+  <si>
+    <t>validation fails: phone field error returned</t>
+  </si>
+  <si>
+    <t>EC-5</t>
+  </si>
+  <si>
+    <t>valid member data with dateOfBirth field omitted</t>
+  </si>
+  <si>
+    <t>validation fails: dateOfBirth field error returned</t>
+  </si>
+  <si>
+    <t>EC-6</t>
+  </si>
+  <si>
+    <t>valid member data with password field omitted</t>
+  </si>
+  <si>
+    <t>validation fails: password field error returned</t>
+  </si>
+  <si>
+    <t>EC-7</t>
+  </si>
+  <si>
+    <t>valid member data with membershipStart field omitted</t>
+  </si>
+  <si>
+    <t>validation fails: membershipStart field error returned</t>
+  </si>
+  <si>
+    <t>EC-8</t>
+  </si>
+  <si>
+    <t>valid member data with email set to "invalid"</t>
+  </si>
+  <si>
+    <t>EC-9</t>
+  </si>
+  <si>
+    <t>valid member data with password "securep@ss1!" (no uppercase letter)</t>
+  </si>
+  <si>
+    <t>EC-10</t>
+  </si>
+  <si>
+    <t>valid member data with password "SecurePass!" (no digit)</t>
+  </si>
+  <si>
+    <t>EC-11</t>
+  </si>
+  <si>
+    <t>valid member data with password "SecurePass1" (no special character)</t>
+  </si>
+  <si>
+    <t>EC-12</t>
+  </si>
+  <si>
+    <t>valid member data with phone "0712345678" (no country code)</t>
+  </si>
+  <si>
+    <t>EC-13</t>
+  </si>
+  <si>
+    <t>valid member data with dateOfBirth "15-01-1990" (DD-MM-YYYY, wrong format)</t>
+  </si>
+  <si>
+    <t>EC-14</t>
+  </si>
+  <si>
+    <t>valid member data with dateOfBirth "2099-01-01" (future date)</t>
+  </si>
+  <si>
+    <t>EC-15</t>
+  </si>
+  <si>
+    <t>valid member data with membershipStart "2099-01-01" (future date)</t>
+  </si>
+  <si>
+    <t>validation passes, member created successfully with membershipStart set to 2099-01-01</t>
+  </si>
+  <si>
+    <t>EC-16</t>
+  </si>
+  <si>
+    <t>valid member data with membershipStart "01/01/2024" (MM/DD/YYYY, wrong format)</t>
+  </si>
+  <si>
+    <t>EC-17</t>
+  </si>
+  <si>
+    <t>valid member data with fullName "         " (whitespace-only)</t>
+  </si>
+  <si>
+    <t>EC-18</t>
+  </si>
+  <si>
+    <t>valid member data with fullName "  John Doe Test  " (surrounding whitespace)</t>
+  </si>
+  <si>
+    <t>validation passes after trimming, member created successfully</t>
+  </si>
+  <si>
+    <t>EC-19</t>
+  </si>
+  <si>
+    <t>valid member data with email "  john.doe@example.com  " (surrounding whitespace)</t>
+  </si>
+  <si>
+    <t>EC-20</t>
+  </si>
+  <si>
+    <t>valid member data with phone "  +40712345678  " (surrounding whitespace)</t>
+  </si>
+  <si>
+    <t>EC-21</t>
+  </si>
+  <si>
+    <t>all required member fields valid, a duplicate email conflict occurs</t>
+  </si>
+  <si>
+    <t>operation fails with message "Email already registered"</t>
+  </si>
+  <si>
+    <t>EC-22</t>
+  </si>
+  <si>
+    <t>all required member fields valid, a database transaction failure occurs</t>
+  </si>
+  <si>
+    <t>operation fails with message "DB failure"</t>
+  </si>
+  <si>
+    <t>Number BVA</t>
+  </si>
+  <si>
+    <t>BVA Test Case</t>
   </si>
   <si>
     <t>fullName length</t>
   </si>
   <si>
-    <t>fullName ≥ 8 chars</t>
-  </si>
-  <si>
-    <t>fullName &lt; 8 chars → validation error</t>
-  </si>
-  <si>
-    <t>email format</t>
-  </si>
-  <si>
-    <t>valid email</t>
-  </si>
-  <si>
-    <t>invalid email → validation error</t>
-  </si>
-  <si>
-    <t>phone format</t>
-  </si>
-  <si>
-    <t>E.164 phone</t>
-  </si>
-  <si>
-    <t>invalid phone → validation error</t>
-  </si>
-  <si>
-    <t>service outcome</t>
-  </si>
-  <si>
-    <t>userService.createMember resolves</t>
-  </si>
-  <si>
-    <t>service throws ConflictError → failure with message</t>
-  </si>
-  <si>
-    <t>service throws Error → generic failure</t>
-  </si>
-  <si>
-    <t>No TC</t>
-  </si>
-  <si>
-    <t>EC</t>
-  </si>
-  <si>
-    <t>Input Data</t>
-  </si>
-  <si>
-    <t>Expected</t>
-  </si>
-  <si>
-    <t>Actual Result</t>
-  </si>
-  <si>
-    <t>1,2,4,6,8</t>
-  </si>
-  <si>
-    <t>VALID_MEMBER_INPUT, service resolves MemberWithUser</t>
-  </si>
-  <si>
-    <t>{ success: true, data: MemberWithUser }</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>{ ...VALID_MEMBER_INPUT, fullName: "Jo" }</t>
-  </si>
-  <si>
-    <t>{ success: false, errors defined }</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>{ ...VALID_MEMBER_INPUT, email: "not-an-email" }</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>{ ...VALID_MEMBER_INPUT, phone: "12345" }</t>
-  </si>
-  <si>
-    <t>{ ...VALID_MEMBER_INPUT, dateOfBirth: "not-a-date" }</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>valid input, service throws ConflictError</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "Email already registered" }</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>valid input, service throws Error</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "An unexpected error occurred" }</t>
-  </si>
-  <si>
-    <t>Number BVA</t>
-  </si>
-  <si>
-    <t>BVA Test Case</t>
-  </si>
-  <si>
-    <t>fullName length boundary</t>
-  </si>
-  <si>
-    <t>fullName with 7 chars → invalid</t>
-  </si>
-  <si>
-    <t>fullName with 8 chars → valid</t>
-  </si>
-  <si>
-    <t>fullName with 64 chars → valid</t>
-  </si>
-  <si>
-    <t>fullName with 65 chars → invalid</t>
-  </si>
-  <si>
-    <t>fullName interior</t>
-  </si>
-  <si>
-    <t>fullName with 9 chars → valid (min+1)</t>
-  </si>
-  <si>
-    <t>fullName with 63 chars → valid (max-1)</t>
-  </si>
-  <si>
-    <t>password length boundary</t>
-  </si>
-  <si>
-    <t>password with 9 chars → valid (min+1)</t>
-  </si>
-  <si>
-    <t>password with 63 chars → valid (max-1)</t>
+    <t>7 chars (min - 1): below minimum → invalid; 8 chars (min): at minimum → valid; 9 chars (min + 1): above minimum → valid</t>
+  </si>
+  <si>
+    <t>63 chars (max - 1): below maximum → valid; 64 chars (max): at maximum → valid; 65 chars (max + 1): above maximum → invalid</t>
+  </si>
+  <si>
+    <t>fullName whitespace + trim</t>
+  </si>
+  <si>
+    <t>8 whitespace chars (empty after trim): invalid; 8 real chars + padding (8 chars after trim): valid; 64 real chars + padding (64 chars after trim): valid; 65 real chars + padding (65 chars after trim): invalid</t>
+  </si>
+  <si>
+    <t>password length</t>
+  </si>
+  <si>
+    <t>dateOfBirth boundary</t>
+  </si>
+  <si>
+    <t>yesterday (today - 1 day): strictly before today → valid; today: not before today → invalid; tomorrow (today + 1 day): future → invalid</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>fullName=7 chars</t>
-  </si>
-  <si>
-    <t>{ fullName: "1234567" }</t>
-  </si>
-  <si>
-    <t>success=false, errors.fullName defined</t>
-  </si>
-  <si>
-    <t>fullName=8 chars</t>
-  </si>
-  <si>
-    <t>{ fullName: "12345678" }</t>
-  </si>
-  <si>
-    <t>success=true</t>
-  </si>
-  <si>
-    <t>fullName=64 chars</t>
-  </si>
-  <si>
-    <t>{ fullName: "a".repeat(64) }</t>
-  </si>
-  <si>
-    <t>fullName=65 chars</t>
-  </si>
-  <si>
-    <t>{ fullName: "a".repeat(65) }</t>
-  </si>
-  <si>
-    <t>fullName=9 chars</t>
-  </si>
-  <si>
-    <t>{ fullName: "John Doe1" }</t>
-  </si>
-  <si>
-    <t>fullName=63 chars</t>
-  </si>
-  <si>
-    <t>{ fullName: "j".repeat(63) }</t>
-  </si>
-  <si>
-    <t>password=9 chars</t>
-  </si>
-  <si>
-    <t>{ password: "Pass1@aAb" }</t>
-  </si>
-  <si>
-    <t>password=63 chars</t>
-  </si>
-  <si>
-    <t>{ password: "A1@"+ "a".repeat(60) }</t>
+    <t>BVA-1 (n=7)</t>
+  </si>
+  <si>
+    <t>valid member data with fullName of 7 characters ("A".repeat(7))</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=8)</t>
+  </si>
+  <si>
+    <t>valid member data with fullName of 8 characters ("A".repeat(8))</t>
+  </si>
+  <si>
+    <t>validation passes, member created successfully</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=9)</t>
+  </si>
+  <si>
+    <t>valid member data with fullName of 9 characters ("A".repeat(9))</t>
+  </si>
+  <si>
+    <t>BVA-2 (n=63)</t>
+  </si>
+  <si>
+    <t>valid member data with fullName of 63 characters ("A".repeat(63))</t>
+  </si>
+  <si>
+    <t>BVA-2 (n=64)</t>
+  </si>
+  <si>
+    <t>valid member data with fullName of 64 characters ("A".repeat(64))</t>
+  </si>
+  <si>
+    <t>BVA-2 (n=65)</t>
+  </si>
+  <si>
+    <t>valid member data with fullName of 65 characters ("A".repeat(65))</t>
+  </si>
+  <si>
+    <t>BVA-3 (ws=8)</t>
+  </si>
+  <si>
+    <t>valid member data with fullName of 8 whitespace characters (empty string after trim)</t>
+  </si>
+  <si>
+    <t>BVA-3 (p=8)</t>
+  </si>
+  <si>
+    <t>valid member data with fullName padded to 8 real characters after trimming (" " + "A".repeat(8) + " ")</t>
+  </si>
+  <si>
+    <t>BVA-3 (p=64)</t>
+  </si>
+  <si>
+    <t>valid member data with fullName padded to 64 real characters after trimming (" " + "A".repeat(64) + " ")</t>
+  </si>
+  <si>
+    <t>BVA-3 (p=65)</t>
+  </si>
+  <si>
+    <t>valid member data with fullName padded to 65 real characters after trimming (" " + "A".repeat(65) + " ")</t>
+  </si>
+  <si>
+    <t>BVA-4 (n=7)</t>
+  </si>
+  <si>
+    <t>valid member data with password of 7 characters meeting all rules except minimum length ("P1@aaaa")</t>
+  </si>
+  <si>
+    <t>BVA-4 (n=8)</t>
+  </si>
+  <si>
+    <t>valid member data with password of 8 characters meeting all rules ("P1@aaaaa")</t>
+  </si>
+  <si>
+    <t>BVA-4 (n=9)</t>
+  </si>
+  <si>
+    <t>valid member data with password of 9 characters meeting all rules ("P1@aaaaaa")</t>
+  </si>
+  <si>
+    <t>BVA-5 (n=63)</t>
+  </si>
+  <si>
+    <t>valid member data with password of 63 characters meeting all rules ("P1@" + "a".repeat(60))</t>
+  </si>
+  <si>
+    <t>BVA-5 (n=64)</t>
+  </si>
+  <si>
+    <t>valid member data with password of 64 characters meeting all rules ("P1@" + "a".repeat(61))</t>
+  </si>
+  <si>
+    <t>BVA-5 (n=65)</t>
+  </si>
+  <si>
+    <t>valid member data with password of 65 characters ("P1@" + "a".repeat(62))</t>
+  </si>
+  <si>
+    <t>BVA-6 (yest)</t>
+  </si>
+  <si>
+    <t>valid member data with dateOfBirth set to yesterday (one day before today, YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>BVA-6 (today)</t>
+  </si>
+  <si>
+    <t>valid member data with dateOfBirth set to today (YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>validation fails: dateOfBirth field error returned (not strictly in the past)</t>
+  </si>
+  <si>
+    <t>BVA-6 (tmrw)</t>
+  </si>
+  <si>
+    <t>valid member data with dateOfBirth set to tomorrow (one day after today, YYYY-MM-DD)</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -279,87 +505,24 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EP-1</t>
-  </si>
-  <si>
-    <t>Valid input, service resolves</t>
-  </si>
-  <si>
-    <t>success=true, MemberWithUser returned</t>
-  </si>
-  <si>
-    <t>EP-2</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>fullName 7 chars</t>
-  </si>
-  <si>
-    <t>success=false, errors defined</t>
-  </si>
-  <si>
     <t>BVA-2</t>
   </si>
   <si>
-    <t>fullName 8 chars (boundary valid)</t>
-  </si>
-  <si>
-    <t>EP-3</t>
-  </si>
-  <si>
-    <t>Invalid email</t>
-  </si>
-  <si>
-    <t>EP-4</t>
-  </si>
-  <si>
-    <t>Invalid phone</t>
-  </si>
-  <si>
-    <t>EP-6</t>
-  </si>
-  <si>
-    <t>Valid, service throws ConflictError</t>
-  </si>
-  <si>
-    <t>success=false, message from error</t>
-  </si>
-  <si>
-    <t>EP-7</t>
-  </si>
-  <si>
-    <t>Valid, service throws unexpected Error</t>
-  </si>
-  <si>
-    <t>success=false, message="An unexpected error occurred"</t>
+    <t>BVA-3</t>
+  </si>
+  <si>
+    <t>BVA-4</t>
   </si>
   <si>
     <t>BVA-5</t>
   </si>
   <si>
-    <t>fullName 9 chars</t>
-  </si>
-  <si>
     <t>BVA-6</t>
   </si>
   <si>
-    <t>fullName 63 chars</t>
-  </si>
-  <si>
-    <t>BVA-7</t>
-  </si>
-  <si>
-    <t>password 9 chars</t>
-  </si>
-  <si>
-    <t>BVA-8</t>
-  </si>
-  <si>
-    <t>password 63 chars</t>
-  </si>
-  <si>
     <t>Testing</t>
   </si>
   <si>
@@ -390,16 +553,13 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>MEM-01</t>
+    <t>CTRL-03</t>
   </si>
   <si>
     <t>n/a</t>
   </si>
   <si>
     <t>not yet</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -915,7 +1075,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -959,10 +1119,10 @@
         <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -970,7 +1130,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
@@ -984,13 +1144,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -998,13 +1158,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1012,13 +1172,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1026,13 +1186,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1040,13 +1200,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1054,13 +1214,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1068,13 +1228,181 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1085,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1097,19 +1425,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1117,16 +1445,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1134,16 +1462,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1151,16 +1479,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1168,16 +1496,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1185,16 +1513,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1202,16 +1530,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1219,16 +1547,271 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>51</v>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1239,7 +1822,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1249,13 +1832,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>53</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1263,87 +1846,65 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>54</v>
+        <v>111</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
+      <c r="A3" s="1">
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>111</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>56</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>114</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>57</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
+      <c r="A5" s="1">
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>60</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>6</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1354,7 +1915,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1366,19 +1927,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1386,16 +1947,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1403,16 +1964,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1420,16 +1981,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1437,16 +1998,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1454,16 +2015,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>76</v>
+        <v>129</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1471,16 +2032,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1488,16 +2049,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1505,16 +2066,203 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>83</v>
+        <v>136</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E12" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>71</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1525,7 +2273,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1538,22 +2286,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>84</v>
+        <v>160</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1561,19 +2309,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1581,19 +2329,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1601,19 +2349,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1621,19 +2369,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1641,19 +2389,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1661,19 +2409,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1681,19 +2429,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>104</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1701,19 +2449,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1721,19 +2469,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>107</v>
+        <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1741,19 +2489,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1761,19 +2509,619 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>111</v>
+        <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F12" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>71</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1801,16 +3149,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1818,45 +3166,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>117</v>
+        <v>172</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>122</v>
+        <v>177</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>117</v>
+        <v>172</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>119</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>123</v>
+      <c r="A3" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="B3" s="1">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="C3" s="1">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1865,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>124</v>
+        <v>179</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>125</v>
+        <v>180</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>126</v>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
